--- a/IC-Product-Backlog-Example-11532_ES.xlsx
+++ b/IC-Product-Backlog-Example-11532_ES.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\usuario\Documents\GitHub\tallercusi\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{299B342B-05B7-4F8E-A6DA-9C27340F22C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD72ED41-A57B-4DED-8464-ABE4E346B857}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="19440" windowHeight="14880" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
